--- a/Employee_Reports_wi48/Arnel Butiu Guevarra Q0158.xlsx
+++ b/Employee_Reports_wi48/Arnel Butiu Guevarra Q0158.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -789,53 +789,53 @@
       <c r="K7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Weight scales (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-M-013</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>12-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>12-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>08-Apr-2028</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>632</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1399,11 +1399,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1448,11 +1448,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1584,11 +1584,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1599,53 +1599,53 @@
       <c r="K24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Incident Escalation Process(LSME-IMS-SOP-021 ) (SOPs)</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-021</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>14-Jul-2025</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>14-Jul-2026</t>
         </is>
       </c>
-      <c r="H25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="H25" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>-95</v>
+        <v>-98</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
@@ -1754,9 +1754,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
           <t>10-Apr-2025</t>
@@ -1768,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-94</v>
+        <v>-97</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1817,11 +1829,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1866,11 +1878,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1915,11 +1927,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1964,11 +1976,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2013,11 +2025,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2050,11 +2062,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2087,11 +2099,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2136,11 +2148,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2185,11 +2197,11 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
@@ -2222,11 +2234,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2259,11 +2271,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2296,11 +2308,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2333,11 +2345,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2370,11 +2382,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -3075,7 +3087,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3104,7 +3116,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3133,7 +3145,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3162,7 +3174,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3191,7 +3203,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3220,7 +3232,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3249,7 +3261,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3278,7 +3290,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3307,7 +3319,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3336,7 +3348,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3365,7 +3377,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3394,7 +3406,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -3423,7 +3435,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7963</v>
+        <v>7960</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -3452,7 +3464,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7963</v>
+        <v>7960</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -3481,7 +3493,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7948</v>
+        <v>7945</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -3510,7 +3522,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -3539,7 +3551,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3568,7 +3580,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3597,7 +3609,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -3626,7 +3638,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7948</v>
+        <v>7945</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3655,7 +3667,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7953</v>
+        <v>7950</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
